--- a/mosip_master/xlsx/dynamic_field.xlsx
+++ b/mosip_master/xlsx/dynamic_field.xlsx
@@ -1,33 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mahesh.Binayak\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\Sao-Tome-mosip-master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{172209B5-9444-45AE-8B0E-D1F4308381C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="6720" tabRatio="500"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$66</definedName>
   </definedNames>
-  <calcPr calcId="162913" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="96">
   <si>
     <t>id</t>
   </si>
@@ -294,13 +303,6 @@
 	}</t>
   </si>
   <si>
-    <t xml:space="preserve">
-	{
-		"code": "OTH",
-		"value": "Others"
-	}</t>
-  </si>
-  <si>
     <t>residenceStatus</t>
   </si>
   <si>
@@ -436,27 +438,6 @@
   <si>
     <t xml:space="preserve">
 	{
-		"code": "MLE",
-		"value": "Mâle"
-	}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-	{
-		"code": "FLE",
-		"value": "Femelle"
-	}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-	{
-		"code": "OTH",
-		"value": "Autres"
-	}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-	{
 		"code": "FR",
 		"value": "Étrangère"
 	}</t>
@@ -469,210 +450,138 @@
 	}</t>
   </si>
   <si>
+    <t>{"value":"عربي","code":"ara"}</t>
+  </si>
+  <si>
+    <t>por</t>
+  </si>
+  <si>
+    <t>{"value":"Português","code":"por"}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+	{
+		"code": "MLE",
+		"value": "Macho"
+	}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+	{
+		"code": "FLE",
+		"value": "Fêmea"
+	}</t>
+  </si>
+  <si>
     <t xml:space="preserve">
 	{
 		"code": "101",
-		"value": "أ",
-	}</t>
-  </si>
-  <si>
-    <t>ara</t>
+		"value": "Solteiro(a)"
+	}</t>
   </si>
   <si>
     <t xml:space="preserve">
 	{
 		"code": "102",
-		"value": "أ +",
+		"value": "Casado(a)"
 	}</t>
   </si>
   <si>
     <t xml:space="preserve">
 	{
 		"code": "103",
-		"value": "أ-",
+		"value": "Divorciado(a)"
 	}</t>
   </si>
   <si>
     <t xml:space="preserve">
 	{
 		"code": "104",
-		"value": "ب",
-	}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-	{
-		"code": "105",
-		"value": "ب +",
-	}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-	{
-		"code": "106",
-		"value": "ب-",
-	}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-	{
-		"code": "110",
-		"value": "ا",
-	}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-	{
-		"code": "112",
-		"value": "س-"
-	}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-	{
-		"code": "113",
-		"value": "لا اعرف"
-	}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-	{
-		"code": "114",
-		"value": "غير قابل للتطبيق"
-	}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-	{
-		"code": "101",
-		"value": "غير مرتبطة
-"
-	}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-	{
-		"code": "102",
-		"value": "زوجت"
+		"value": "Viúvo(a)"
 	}</t>
   </si>
   <si>
     <t xml:space="preserve">
 	{
 		"code": "103",
-		"value": "الأرامل"
+		"value": "Divorced"
 	}</t>
   </si>
   <si>
     <t xml:space="preserve">
 	{
 		"code": "104",
-		"value": "مطلق"
-	}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-	{
-		"code": "105",
-		"value": "مطلق من الناحية القانونية
-"
-	}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-	{
-		"code": "106",
-		"value": "ملغاة"
-	}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-	{
-		"code": "107",
-		"value": "مبطل"
-	}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-	{
-		"code": "Document-based",
-		"value": "مستند إلى المستند"
-	}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-	{
-		"code": "Introducer-based",
-		"value": "المعرف القائم"
-	}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-	{
-		"code": "101",
-		"value": "يلتقط"
-	}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-	{
-		"code": "102",
-		"value": "التسليم إلى العنوان الدائم"
-	}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-	{
-		"code": "103",
-		"value": "التسليم إلى العنوان الحالي"
-	}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-	{
-		"code": "MLE",
-		"value": "ذكر"
-	}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-	{
-		"code": "FLE",
-		"value": "أنثى"
-	}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-	{
-		"code": "OTH",
-		"value": "آحرون"
-	}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-	{
-		"code": "FR",
-		"value": "أجنبي"
-	}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-	{
-		"code": "NFR",
-		"value": "غير أجنبي"
-	}</t>
-  </si>
-  <si>
-    <t>{"value":"عربى","code":"ara"}</t>
-  </si>
-  <si>
-    <t>{"value":"عربي","code":"ara"}</t>
+		"value": "Widowed"
+	}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+	{
+		"code": "RE",
+		"value": "Refugee"
+	}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+	{
+		"code": "MT",
+		"value": "Migrant"
+	}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+	{
+		"code": "DI",
+		"value": "Internally Displaced"
+	}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+	{
+		"code": "CO",
+		"value": "Citizen"
+	}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+	{
+		"code": "ER",
+		"value": "Foreigner"
+	}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+	{
+		"code": "CO",
+		"value": "Cidadão"
+	}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+	{
+		"code": "ER",
+		"value": "Etranger"
+	}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+	{
+		"code": "RE",
+		"value": "Refugié"
+	}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+	{
+		"code": "DI",
+		"value": "Deplacé interne"
+	}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
@@ -726,12 +635,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1014,22 +938,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I103"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:I84"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" customWidth="1"/>
-    <col min="4" max="4" width="21.5703125" customWidth="1"/>
-    <col min="5" max="5" width="32.5703125" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.6328125" customWidth="1"/>
+    <col min="4" max="4" width="21.54296875" customWidth="1"/>
+    <col min="5" max="5" width="32.54296875" customWidth="1"/>
+    <col min="6" max="6" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1058,7 +983,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>10001</v>
       </c>
@@ -1088,7 +1013,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>10002</v>
       </c>
@@ -1118,7 +1043,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>10003</v>
       </c>
@@ -1148,7 +1073,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>10004</v>
       </c>
@@ -1178,7 +1103,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>10005</v>
       </c>
@@ -1208,7 +1133,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>10006</v>
       </c>
@@ -1238,7 +1163,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>10007</v>
       </c>
@@ -1268,7 +1193,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>10008</v>
       </c>
@@ -1298,7 +1223,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>10009</v>
       </c>
@@ -1328,7 +1253,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10010</v>
       </c>
@@ -1358,7 +1283,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>10011</v>
       </c>
@@ -1388,7 +1313,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>10012</v>
       </c>
@@ -1418,7 +1343,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>10013</v>
       </c>
@@ -1448,7 +1373,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>10014</v>
       </c>
@@ -1478,7 +1403,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>10015</v>
       </c>
@@ -1508,7 +1433,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>10016</v>
       </c>
@@ -1538,7 +1463,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>10017</v>
       </c>
@@ -1568,7 +1493,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>10018</v>
       </c>
@@ -1598,7 +1523,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>10019</v>
       </c>
@@ -1628,7 +1553,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>10020</v>
       </c>
@@ -1658,7 +1583,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>10021</v>
       </c>
@@ -1688,7 +1613,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>10022</v>
       </c>
@@ -1718,7 +1643,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>10023</v>
       </c>
@@ -1748,7 +1673,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>10024</v>
       </c>
@@ -1778,7 +1703,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>10025</v>
       </c>
@@ -1808,7 +1733,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>10026</v>
       </c>
@@ -1838,7 +1763,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>10027</v>
       </c>
@@ -1868,7 +1793,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>10028</v>
       </c>
@@ -1898,45 +1823,45 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>10029</v>
+        <v>10030</v>
       </c>
       <c r="B30" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C30" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D30" t="s">
         <v>11</v>
       </c>
       <c r="E30" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F30" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" s="3" t="b">
+        <f>TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="H30" t="s">
+        <v>14</v>
+      </c>
+      <c r="I30" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>10031</v>
+      </c>
+      <c r="B31" t="s">
         <v>51</v>
       </c>
-      <c r="F30" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H30" t="s">
-        <v>14</v>
-      </c>
-      <c r="I30" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>10030</v>
-      </c>
-      <c r="B31" t="s">
-        <v>52</v>
-      </c>
       <c r="C31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D31" t="s">
         <v>11</v>
@@ -1958,105 +1883,105 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>10031</v>
-      </c>
-      <c r="B32" t="s">
-        <v>52</v>
-      </c>
-      <c r="C32" t="s">
-        <v>52</v>
-      </c>
-      <c r="D32" t="s">
+    <row r="32" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="A32" s="2">
+        <v>10310</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E32" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32" s="3" t="b">
+        <f>TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="A33" s="2">
+        <v>10313</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F32" t="s">
-        <v>13</v>
-      </c>
-      <c r="G32" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H32" t="s">
-        <v>14</v>
-      </c>
-      <c r="I32" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
-        <v>10310</v>
-      </c>
-      <c r="B33" s="2" t="s">
+      <c r="C33" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="D33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G33" s="3" t="b">
+        <f>TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="2">
+        <v>10317</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
-        <v>10313</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" s="2" t="s">
+      <c r="F34" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G34" s="3" t="b">
+        <f>TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="2">
+        <v>10319</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G34" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
-        <v>10317</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>11</v>
@@ -2065,7 +1990,7 @@
         <v>57</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G35" s="3" t="b">
         <f>TRUE()</f>
@@ -2078,39 +2003,39 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
-        <v>10319</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C36" s="2" t="s">
+    <row r="36" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>10063</v>
+      </c>
+      <c r="B36" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" t="s">
         <v>59</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="G36" s="3" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H36" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="H36" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>10063</v>
+        <v>10064</v>
       </c>
       <c r="B37" t="s">
         <v>9</v>
@@ -2122,10 +2047,10 @@
         <v>11</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F37" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G37" s="3" t="b">
         <f>TRUE()</f>
@@ -2138,9 +2063,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>10064</v>
+        <v>10065</v>
       </c>
       <c r="B38" t="s">
         <v>9</v>
@@ -2152,10 +2077,10 @@
         <v>11</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G38" s="3" t="b">
         <f>TRUE()</f>
@@ -2168,9 +2093,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>10065</v>
+        <v>10066</v>
       </c>
       <c r="B39" t="s">
         <v>9</v>
@@ -2182,10 +2107,10 @@
         <v>11</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F39" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G39" s="3" t="b">
         <f>TRUE()</f>
@@ -2198,9 +2123,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>10066</v>
+        <v>10067</v>
       </c>
       <c r="B40" t="s">
         <v>9</v>
@@ -2212,10 +2137,10 @@
         <v>11</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G40" s="3" t="b">
         <f>TRUE()</f>
@@ -2228,9 +2153,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>10067</v>
+        <v>10068</v>
       </c>
       <c r="B41" t="s">
         <v>9</v>
@@ -2242,10 +2167,10 @@
         <v>11</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F41" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G41" s="3" t="b">
         <f>TRUE()</f>
@@ -2258,9 +2183,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>10068</v>
+        <v>10069</v>
       </c>
       <c r="B42" t="s">
         <v>9</v>
@@ -2272,10 +2197,10 @@
         <v>11</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F42" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G42" s="3" t="b">
         <f>TRUE()</f>
@@ -2288,9 +2213,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>10069</v>
+        <v>10070</v>
       </c>
       <c r="B43" t="s">
         <v>9</v>
@@ -2302,10 +2227,10 @@
         <v>11</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F43" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G43" s="3" t="b">
         <f>TRUE()</f>
@@ -2318,9 +2243,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>10070</v>
+        <v>10071</v>
       </c>
       <c r="B44" t="s">
         <v>9</v>
@@ -2332,10 +2257,10 @@
         <v>11</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F44" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G44" s="3" t="b">
         <f>TRUE()</f>
@@ -2348,9 +2273,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>10071</v>
+        <v>10072</v>
       </c>
       <c r="B45" t="s">
         <v>9</v>
@@ -2362,10 +2287,10 @@
         <v>11</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F45" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G45" s="3" t="b">
         <f>TRUE()</f>
@@ -2378,9 +2303,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>10072</v>
+        <v>10073</v>
       </c>
       <c r="B46" t="s">
         <v>9</v>
@@ -2392,10 +2317,10 @@
         <v>11</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F46" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G46" s="3" t="b">
         <f>TRUE()</f>
@@ -2408,9 +2333,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47">
-        <v>10073</v>
+        <v>10074</v>
       </c>
       <c r="B47" t="s">
         <v>9</v>
@@ -2422,10 +2347,10 @@
         <v>11</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F47" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G47" s="3" t="b">
         <f>TRUE()</f>
@@ -2438,9 +2363,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48">
-        <v>10074</v>
+        <v>10075</v>
       </c>
       <c r="B48" t="s">
         <v>9</v>
@@ -2452,10 +2377,10 @@
         <v>11</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F48" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G48" s="3" t="b">
         <f>TRUE()</f>
@@ -2468,9 +2393,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49">
-        <v>10075</v>
+        <v>10076</v>
       </c>
       <c r="B49" t="s">
         <v>9</v>
@@ -2485,7 +2410,7 @@
         <v>61</v>
       </c>
       <c r="F49" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G49" s="3" t="b">
         <f>TRUE()</f>
@@ -2498,15 +2423,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50">
-        <v>10076</v>
+        <v>10077</v>
       </c>
       <c r="B50" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C50" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D50" t="s">
         <v>11</v>
@@ -2515,7 +2440,7 @@
         <v>62</v>
       </c>
       <c r="F50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G50" s="3" t="b">
         <f>TRUE()</f>
@@ -2528,9 +2453,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51">
-        <v>10077</v>
+        <v>10078</v>
       </c>
       <c r="B51" t="s">
         <v>29</v>
@@ -2545,7 +2470,7 @@
         <v>63</v>
       </c>
       <c r="F51" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G51" s="3" t="b">
         <f>TRUE()</f>
@@ -2558,9 +2483,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52">
-        <v>10078</v>
+        <v>10079</v>
       </c>
       <c r="B52" t="s">
         <v>29</v>
@@ -2575,7 +2500,7 @@
         <v>64</v>
       </c>
       <c r="F52" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G52" s="3" t="b">
         <f>TRUE()</f>
@@ -2588,9 +2513,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53">
-        <v>10079</v>
+        <v>10080</v>
       </c>
       <c r="B53" t="s">
         <v>29</v>
@@ -2605,7 +2530,7 @@
         <v>65</v>
       </c>
       <c r="F53" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G53" s="3" t="b">
         <f>TRUE()</f>
@@ -2618,9 +2543,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54">
-        <v>10080</v>
+        <v>10081</v>
       </c>
       <c r="B54" t="s">
         <v>29</v>
@@ -2635,7 +2560,7 @@
         <v>66</v>
       </c>
       <c r="F54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G54" s="3" t="b">
         <f>TRUE()</f>
@@ -2648,9 +2573,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55">
-        <v>10081</v>
+        <v>10082</v>
       </c>
       <c r="B55" t="s">
         <v>29</v>
@@ -2665,7 +2590,7 @@
         <v>67</v>
       </c>
       <c r="F55" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G55" s="3" t="b">
         <f>TRUE()</f>
@@ -2678,9 +2603,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56">
-        <v>10082</v>
+        <v>10083</v>
       </c>
       <c r="B56" t="s">
         <v>29</v>
@@ -2695,7 +2620,7 @@
         <v>68</v>
       </c>
       <c r="F56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G56" s="3" t="b">
         <f>TRUE()</f>
@@ -2708,15 +2633,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57">
-        <v>10083</v>
+        <v>10084</v>
       </c>
       <c r="B57" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C57" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D57" t="s">
         <v>11</v>
@@ -2725,7 +2650,7 @@
         <v>69</v>
       </c>
       <c r="F57" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G57" s="3" t="b">
         <f>TRUE()</f>
@@ -2738,9 +2663,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58">
-        <v>10084</v>
+        <v>10085</v>
       </c>
       <c r="B58" t="s">
         <v>38</v>
@@ -2755,7 +2680,7 @@
         <v>70</v>
       </c>
       <c r="F58" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G58" s="3" t="b">
         <f>TRUE()</f>
@@ -2768,15 +2693,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59">
-        <v>10085</v>
+        <v>10086</v>
       </c>
       <c r="B59" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C59" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D59" t="s">
         <v>11</v>
@@ -2785,7 +2710,7 @@
         <v>71</v>
       </c>
       <c r="F59" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G59" s="3" t="b">
         <f>TRUE()</f>
@@ -2798,9 +2723,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60">
-        <v>10086</v>
+        <v>10087</v>
       </c>
       <c r="B60" t="s">
         <v>42</v>
@@ -2815,7 +2740,7 @@
         <v>72</v>
       </c>
       <c r="F60" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G60" s="3" t="b">
         <f>TRUE()</f>
@@ -2828,9 +2753,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61">
-        <v>10087</v>
+        <v>10088</v>
       </c>
       <c r="B61" t="s">
         <v>42</v>
@@ -2845,7 +2770,7 @@
         <v>73</v>
       </c>
       <c r="F61" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G61" s="3" t="b">
         <f>TRUE()</f>
@@ -2858,24 +2783,24 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A62">
-        <v>10088</v>
+        <v>10089</v>
       </c>
       <c r="B62" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C62" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D62" t="s">
         <v>11</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F62" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="G62" s="3" t="b">
         <f>TRUE()</f>
@@ -2888,9 +2813,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A63">
-        <v>10089</v>
+        <v>10090</v>
       </c>
       <c r="B63" t="s">
         <v>47</v>
@@ -2902,1212 +2827,640 @@
         <v>11</v>
       </c>
       <c r="E63" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F63" t="s">
+        <v>77</v>
+      </c>
+      <c r="G63" s="3" t="b">
+        <f>TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="H63" t="s">
+        <v>14</v>
+      </c>
+      <c r="I63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>10092</v>
+      </c>
+      <c r="B64" t="s">
+        <v>51</v>
+      </c>
+      <c r="C64" t="s">
+        <v>51</v>
+      </c>
+      <c r="D64" t="s">
+        <v>11</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F64" t="s">
+        <v>59</v>
+      </c>
+      <c r="G64" s="3" t="b">
+        <f>TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="H64" t="s">
+        <v>14</v>
+      </c>
+      <c r="I64" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>10093</v>
+      </c>
+      <c r="B65" t="s">
+        <v>51</v>
+      </c>
+      <c r="C65" t="s">
+        <v>51</v>
+      </c>
+      <c r="D65" t="s">
+        <v>11</v>
+      </c>
+      <c r="E65" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F63" t="s">
-        <v>60</v>
-      </c>
-      <c r="G63" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H63" t="s">
-        <v>14</v>
-      </c>
-      <c r="I63" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A64">
-        <v>10090</v>
-      </c>
-      <c r="B64" t="s">
-        <v>47</v>
-      </c>
-      <c r="C64" t="s">
-        <v>48</v>
-      </c>
-      <c r="D64" t="s">
-        <v>11</v>
-      </c>
-      <c r="E64" s="2" t="s">
+      <c r="F65" t="s">
+        <v>59</v>
+      </c>
+      <c r="G65" s="3" t="b">
+        <f>TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="H65" t="s">
+        <v>14</v>
+      </c>
+      <c r="I65" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>10127</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E66" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F64" t="s">
-        <v>60</v>
-      </c>
-      <c r="G64" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H64" t="s">
-        <v>14</v>
-      </c>
-      <c r="I64" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A65">
-        <v>10091</v>
-      </c>
-      <c r="B65" t="s">
-        <v>47</v>
-      </c>
-      <c r="C65" t="s">
-        <v>48</v>
-      </c>
-      <c r="D65" t="s">
-        <v>11</v>
-      </c>
-      <c r="E65" s="2" t="s">
+      <c r="F66" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G66" s="3" t="b">
+        <f>TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A67" s="4">
+        <v>10015</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G67" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H67" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I67" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A68" s="4">
+        <v>10016</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G68" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I68" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A69" s="4">
+        <v>10017</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G69" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H69" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I69" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A70" s="4">
+        <v>10018</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G70" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H70" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I70" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A71" s="7">
+        <v>10077</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="F71" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F65" t="s">
-        <v>60</v>
-      </c>
-      <c r="G65" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H65" t="s">
-        <v>14</v>
-      </c>
-      <c r="I65" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <v>10092</v>
-      </c>
-      <c r="B66" t="s">
-        <v>52</v>
-      </c>
-      <c r="C66" t="s">
-        <v>52</v>
-      </c>
-      <c r="D66" t="s">
-        <v>11</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F66" t="s">
-        <v>60</v>
-      </c>
-      <c r="G66" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H66" t="s">
-        <v>14</v>
-      </c>
-      <c r="I66" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A67">
-        <v>10093</v>
-      </c>
-      <c r="B67" t="s">
-        <v>52</v>
-      </c>
-      <c r="C67" t="s">
-        <v>52</v>
-      </c>
-      <c r="D67" t="s">
-        <v>11</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F67" t="s">
-        <v>60</v>
-      </c>
-      <c r="G67" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H67" t="s">
-        <v>14</v>
-      </c>
-      <c r="I67" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A68">
-        <v>10094</v>
-      </c>
-      <c r="B68" t="s">
-        <v>9</v>
-      </c>
-      <c r="C68" t="s">
-        <v>10</v>
-      </c>
-      <c r="D68" t="s">
-        <v>11</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F68" t="s">
-        <v>81</v>
-      </c>
-      <c r="G68" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H68" t="s">
-        <v>14</v>
-      </c>
-      <c r="I68" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A69">
+      <c r="G71" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H71" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I71" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A72" s="7">
+        <v>10078</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G72" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H72" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I72" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A73" s="7">
+        <v>10079</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="F73" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G73" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H73" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I73" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A74" s="7">
+        <v>10080</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G74" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H74" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I74" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A75" s="10">
+        <v>10085</v>
+      </c>
+      <c r="B75" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C75" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D75" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E75" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="F75" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G75" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H75" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I75" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A76" s="10">
+        <v>10086</v>
+      </c>
+      <c r="B76" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C76" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D76" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E76" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="F76" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G76" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H76" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I76" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A77" s="10">
+        <v>10087</v>
+      </c>
+      <c r="B77" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C77" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D77" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E77" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="F77" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G77" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H77" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I77" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" s="10" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A78" s="10">
+        <v>10088</v>
+      </c>
+      <c r="B78" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C78" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D78" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E78" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="F78" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G78" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H78" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I78" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A79" s="10">
+        <v>10089</v>
+      </c>
+      <c r="B79" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C79" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D79" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E79" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="F79" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G79" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H79" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I79" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A80" s="10">
         <v>10095</v>
       </c>
-      <c r="B69" t="s">
-        <v>9</v>
-      </c>
-      <c r="C69" t="s">
-        <v>10</v>
-      </c>
-      <c r="D69" t="s">
-        <v>11</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F69" t="s">
-        <v>81</v>
-      </c>
-      <c r="G69" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H69" t="s">
-        <v>14</v>
-      </c>
-      <c r="I69" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A70">
-        <v>10096</v>
-      </c>
-      <c r="B70" t="s">
-        <v>9</v>
-      </c>
-      <c r="C70" t="s">
-        <v>10</v>
-      </c>
-      <c r="D70" t="s">
-        <v>11</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F70" t="s">
-        <v>81</v>
-      </c>
-      <c r="G70" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H70" t="s">
-        <v>14</v>
-      </c>
-      <c r="I70" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A71">
-        <v>10097</v>
-      </c>
-      <c r="B71" t="s">
-        <v>9</v>
-      </c>
-      <c r="C71" t="s">
-        <v>10</v>
-      </c>
-      <c r="D71" t="s">
-        <v>11</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F71" t="s">
-        <v>81</v>
-      </c>
-      <c r="G71" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H71" t="s">
-        <v>14</v>
-      </c>
-      <c r="I71" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A72">
-        <v>10098</v>
-      </c>
-      <c r="B72" t="s">
-        <v>9</v>
-      </c>
-      <c r="C72" t="s">
-        <v>10</v>
-      </c>
-      <c r="D72" t="s">
-        <v>11</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F72" t="s">
-        <v>81</v>
-      </c>
-      <c r="G72" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H72" t="s">
-        <v>14</v>
-      </c>
-      <c r="I72" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A73">
-        <v>10099</v>
-      </c>
-      <c r="B73" t="s">
-        <v>9</v>
-      </c>
-      <c r="C73" t="s">
-        <v>10</v>
-      </c>
-      <c r="D73" t="s">
-        <v>11</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F73" t="s">
-        <v>81</v>
-      </c>
-      <c r="G73" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H73" t="s">
-        <v>14</v>
-      </c>
-      <c r="I73" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A74">
-        <v>10100</v>
-      </c>
-      <c r="B74" t="s">
-        <v>9</v>
-      </c>
-      <c r="C74" t="s">
-        <v>10</v>
-      </c>
-      <c r="D74" t="s">
-        <v>11</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F74" t="s">
-        <v>81</v>
-      </c>
-      <c r="G74" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H74" t="s">
-        <v>14</v>
-      </c>
-      <c r="I74" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A75">
-        <v>10101</v>
-      </c>
-      <c r="B75" t="s">
-        <v>9</v>
-      </c>
-      <c r="C75" t="s">
-        <v>10</v>
-      </c>
-      <c r="D75" t="s">
-        <v>11</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F75" t="s">
-        <v>81</v>
-      </c>
-      <c r="G75" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H75" t="s">
-        <v>14</v>
-      </c>
-      <c r="I75" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A76">
-        <v>10102</v>
-      </c>
-      <c r="B76" t="s">
-        <v>9</v>
-      </c>
-      <c r="C76" t="s">
-        <v>10</v>
-      </c>
-      <c r="D76" t="s">
-        <v>11</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F76" t="s">
-        <v>81</v>
-      </c>
-      <c r="G76" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H76" t="s">
-        <v>14</v>
-      </c>
-      <c r="I76" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A77">
-        <v>10103</v>
-      </c>
-      <c r="B77" t="s">
-        <v>9</v>
-      </c>
-      <c r="C77" t="s">
-        <v>10</v>
-      </c>
-      <c r="D77" t="s">
-        <v>11</v>
-      </c>
-      <c r="E77" s="2" t="s">
+      <c r="B80" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C80" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D80" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E80" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="F80" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G80" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H80" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I80" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A81" s="10">
+        <v>10095</v>
+      </c>
+      <c r="B81" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C81" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D81" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E81" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="F81" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G81" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H81" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I81" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A82" s="10">
+        <v>10095</v>
+      </c>
+      <c r="B82" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C82" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D82" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E82" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="F77" t="s">
-        <v>81</v>
-      </c>
-      <c r="G77" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H77" t="s">
-        <v>14</v>
-      </c>
-      <c r="I77" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A78">
-        <v>10104</v>
-      </c>
-      <c r="B78" t="s">
-        <v>9</v>
-      </c>
-      <c r="C78" t="s">
-        <v>10</v>
-      </c>
-      <c r="D78" t="s">
-        <v>11</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F78" t="s">
-        <v>81</v>
-      </c>
-      <c r="G78" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H78" t="s">
-        <v>14</v>
-      </c>
-      <c r="I78" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A79">
-        <v>10105</v>
-      </c>
-      <c r="B79" t="s">
-        <v>9</v>
-      </c>
-      <c r="C79" t="s">
-        <v>10</v>
-      </c>
-      <c r="D79" t="s">
-        <v>11</v>
-      </c>
-      <c r="E79" s="2" t="s">
+      <c r="F82" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G82" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H82" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I82" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A83" s="10">
+        <v>10095</v>
+      </c>
+      <c r="B83" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C83" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D83" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E83" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="F79" t="s">
-        <v>81</v>
-      </c>
-      <c r="G79" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H79" t="s">
-        <v>14</v>
-      </c>
-      <c r="I79" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A80">
-        <v>10106</v>
-      </c>
-      <c r="B80" t="s">
-        <v>9</v>
-      </c>
-      <c r="C80" t="s">
-        <v>10</v>
-      </c>
-      <c r="D80" t="s">
-        <v>11</v>
-      </c>
-      <c r="E80" s="2" t="s">
+      <c r="F83" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G83" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H83" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I83" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A84" s="10">
+        <v>10095</v>
+      </c>
+      <c r="B84" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C84" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D84" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E84" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="F80" t="s">
-        <v>81</v>
-      </c>
-      <c r="G80" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H80" t="s">
-        <v>14</v>
-      </c>
-      <c r="I80" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A81">
-        <v>10107</v>
-      </c>
-      <c r="B81" t="s">
-        <v>9</v>
-      </c>
-      <c r="C81" t="s">
-        <v>10</v>
-      </c>
-      <c r="D81" t="s">
-        <v>11</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F81" t="s">
-        <v>81</v>
-      </c>
-      <c r="G81" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H81" t="s">
-        <v>14</v>
-      </c>
-      <c r="I81" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" ht="90" x14ac:dyDescent="0.25">
-      <c r="A82">
-        <v>10108</v>
-      </c>
-      <c r="B82" t="s">
-        <v>29</v>
-      </c>
-      <c r="C82" t="s">
-        <v>30</v>
-      </c>
-      <c r="D82" t="s">
-        <v>11</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F82" t="s">
-        <v>81</v>
-      </c>
-      <c r="G82" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H82" t="s">
-        <v>14</v>
-      </c>
-      <c r="I82" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A83">
-        <v>10109</v>
-      </c>
-      <c r="B83" t="s">
-        <v>29</v>
-      </c>
-      <c r="C83" t="s">
-        <v>30</v>
-      </c>
-      <c r="D83" t="s">
-        <v>11</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F83" t="s">
-        <v>81</v>
-      </c>
-      <c r="G83" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H83" t="s">
-        <v>14</v>
-      </c>
-      <c r="I83" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A84">
-        <v>10110</v>
-      </c>
-      <c r="B84" t="s">
-        <v>29</v>
-      </c>
-      <c r="C84" t="s">
-        <v>30</v>
-      </c>
-      <c r="D84" t="s">
-        <v>11</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F84" t="s">
-        <v>81</v>
-      </c>
-      <c r="G84" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H84" t="s">
-        <v>14</v>
-      </c>
-      <c r="I84" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A85">
-        <v>10111</v>
-      </c>
-      <c r="B85" t="s">
-        <v>29</v>
-      </c>
-      <c r="C85" t="s">
-        <v>30</v>
-      </c>
-      <c r="D85" t="s">
-        <v>11</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F85" t="s">
-        <v>81</v>
-      </c>
-      <c r="G85" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H85" t="s">
-        <v>14</v>
-      </c>
-      <c r="I85" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" ht="90" x14ac:dyDescent="0.25">
-      <c r="A86">
-        <v>10112</v>
-      </c>
-      <c r="B86" t="s">
-        <v>29</v>
-      </c>
-      <c r="C86" t="s">
-        <v>30</v>
-      </c>
-      <c r="D86" t="s">
-        <v>11</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F86" t="s">
-        <v>81</v>
-      </c>
-      <c r="G86" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H86" t="s">
-        <v>14</v>
-      </c>
-      <c r="I86" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A87">
-        <v>10113</v>
-      </c>
-      <c r="B87" t="s">
-        <v>29</v>
-      </c>
-      <c r="C87" t="s">
-        <v>30</v>
-      </c>
-      <c r="D87" t="s">
-        <v>11</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F87" t="s">
-        <v>81</v>
-      </c>
-      <c r="G87" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H87" t="s">
-        <v>14</v>
-      </c>
-      <c r="I87" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A88">
-        <v>10114</v>
-      </c>
-      <c r="B88" t="s">
-        <v>29</v>
-      </c>
-      <c r="C88" t="s">
-        <v>30</v>
-      </c>
-      <c r="D88" t="s">
-        <v>11</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F88" t="s">
-        <v>81</v>
-      </c>
-      <c r="G88" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H88" t="s">
-        <v>14</v>
-      </c>
-      <c r="I88" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A89">
-        <v>10115</v>
-      </c>
-      <c r="B89" t="s">
-        <v>38</v>
-      </c>
-      <c r="C89" t="s">
-        <v>39</v>
-      </c>
-      <c r="D89" t="s">
-        <v>11</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F89" t="s">
-        <v>81</v>
-      </c>
-      <c r="G89" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H89" t="s">
-        <v>14</v>
-      </c>
-      <c r="I89" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A90">
-        <v>10116</v>
-      </c>
-      <c r="B90" t="s">
-        <v>38</v>
-      </c>
-      <c r="C90" t="s">
-        <v>39</v>
-      </c>
-      <c r="D90" t="s">
-        <v>11</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F90" t="s">
-        <v>81</v>
-      </c>
-      <c r="G90" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H90" t="s">
-        <v>14</v>
-      </c>
-      <c r="I90" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A91">
-        <v>10117</v>
-      </c>
-      <c r="B91" t="s">
-        <v>42</v>
-      </c>
-      <c r="C91" t="s">
-        <v>43</v>
-      </c>
-      <c r="D91" t="s">
-        <v>11</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F91" t="s">
-        <v>81</v>
-      </c>
-      <c r="G91" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H91" t="s">
-        <v>14</v>
-      </c>
-      <c r="I91" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A92">
-        <v>10118</v>
-      </c>
-      <c r="B92" t="s">
-        <v>42</v>
-      </c>
-      <c r="C92" t="s">
-        <v>43</v>
-      </c>
-      <c r="D92" t="s">
-        <v>11</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="F92" t="s">
-        <v>81</v>
-      </c>
-      <c r="G92" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H92" t="s">
-        <v>14</v>
-      </c>
-      <c r="I92" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A93">
-        <v>10119</v>
-      </c>
-      <c r="B93" t="s">
-        <v>42</v>
-      </c>
-      <c r="C93" t="s">
-        <v>43</v>
-      </c>
-      <c r="D93" t="s">
-        <v>11</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F93" t="s">
-        <v>81</v>
-      </c>
-      <c r="G93" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H93" t="s">
-        <v>14</v>
-      </c>
-      <c r="I93" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A94">
-        <v>10120</v>
-      </c>
-      <c r="B94" t="s">
-        <v>47</v>
-      </c>
-      <c r="C94" t="s">
-        <v>48</v>
-      </c>
-      <c r="D94" t="s">
-        <v>11</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F94" t="s">
-        <v>81</v>
-      </c>
-      <c r="G94" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H94" t="s">
-        <v>14</v>
-      </c>
-      <c r="I94" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A95">
-        <v>10121</v>
-      </c>
-      <c r="B95" t="s">
-        <v>47</v>
-      </c>
-      <c r="C95" t="s">
-        <v>48</v>
-      </c>
-      <c r="D95" t="s">
-        <v>11</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F95" t="s">
-        <v>81</v>
-      </c>
-      <c r="G95" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H95" t="s">
-        <v>14</v>
-      </c>
-      <c r="I95" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A96">
-        <v>10122</v>
-      </c>
-      <c r="B96" t="s">
-        <v>47</v>
-      </c>
-      <c r="C96" t="s">
-        <v>48</v>
-      </c>
-      <c r="D96" t="s">
-        <v>11</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="F96" t="s">
-        <v>81</v>
-      </c>
-      <c r="G96" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H96" t="s">
-        <v>14</v>
-      </c>
-      <c r="I96" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A97">
-        <v>10123</v>
-      </c>
-      <c r="B97" t="s">
-        <v>52</v>
-      </c>
-      <c r="C97" t="s">
-        <v>52</v>
-      </c>
-      <c r="D97" t="s">
-        <v>11</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="F97" t="s">
-        <v>81</v>
-      </c>
-      <c r="G97" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H97" t="s">
-        <v>14</v>
-      </c>
-      <c r="I97" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A98">
-        <v>10124</v>
-      </c>
-      <c r="B98" t="s">
-        <v>52</v>
-      </c>
-      <c r="C98" t="s">
-        <v>52</v>
-      </c>
-      <c r="D98" t="s">
-        <v>11</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="F98" t="s">
-        <v>81</v>
-      </c>
-      <c r="G98" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H98" t="s">
-        <v>14</v>
-      </c>
-      <c r="I98" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A99">
-        <v>10125</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="F99" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G99" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H99" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I99" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A100">
-        <v>10126</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G100" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H100" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I100" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A101">
-        <v>10127</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G101" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H101" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I101" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A102">
-        <v>10128</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G102" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H102" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I102" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A103">
-        <v>10129</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F103" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G103" s="3" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I103" s="2" t="s">
+      <c r="F84" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G84" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H84" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I84" s="10" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I103"/>
+  <autoFilter ref="A1:I66" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Gender"/>
+        <filter val="user preferred Language"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/mosip_master/xlsx/dynamic_field.xlsx
+++ b/mosip_master/xlsx/dynamic_field.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\eclipse-workspace\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3958B1B7-913A-430F-A169-A703770CF1DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D9FC4F5-47A5-4FB6-A06F-356858ACB543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$41</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="68">
   <si>
     <t>id</t>
   </si>
@@ -348,6 +348,47 @@
 		"code": "DI",
 		"value": "Deplacé interne"
 	}</t>
+  </si>
+  <si>
+    <t>passportIssuingCountry</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>countryOfCitizenship</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+{
+	"code": "ST",
+	"value": "São Tomé and Príncipe"
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+{
+	"code": "IN",
+	"value": "India"
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+{
+	"code": "US",
+	"value": "United States"
+}
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+{
+	"code": "US",
+	"value": "United States"
+}</t>
   </si>
 </sst>
 </file>
@@ -404,7 +445,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -429,11 +470,42 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="47" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -730,12 +802,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.54296875" style="6" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="3" width="17.6328125" customWidth="1"/>
+    <col min="3" max="3" width="26.26953125" customWidth="1"/>
     <col min="4" max="4" width="21.54296875" customWidth="1"/>
     <col min="5" max="5" width="32.54296875" customWidth="1"/>
     <col min="6" max="6" width="15.6328125" bestFit="1" customWidth="1"/>
@@ -1254,7 +1326,7 @@
         <v>40</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="G18" s="8" t="b">
         <v>1</v>
@@ -1268,7 +1340,7 @@
     </row>
     <row r="19" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
-        <v>10313</v>
+        <v>10312</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>38</v>
@@ -1280,97 +1352,97 @@
         <v>9</v>
       </c>
       <c r="E19" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="A20" s="5">
+        <v>10313</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G19" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="6">
-        <v>10314</v>
-      </c>
-      <c r="B20" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D20" t="s">
-        <v>9</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F20" t="s">
-        <v>41</v>
-      </c>
-      <c r="G20" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H20" t="s">
-        <v>11</v>
-      </c>
-      <c r="I20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="6">
-        <v>10315</v>
-      </c>
-      <c r="B21" t="s">
-        <v>31</v>
-      </c>
-      <c r="C21" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="G20" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="A21" s="5">
+        <v>10311</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F21" t="s">
-        <v>41</v>
-      </c>
-      <c r="G21" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H21" t="s">
-        <v>11</v>
-      </c>
-      <c r="I21" t="s">
+        <v>42</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A22" s="6">
-        <v>10188</v>
+        <v>10314</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D22" t="s">
         <v>9</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="F22" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="G22" s="9" t="b">
         <v>1</v>
@@ -1384,22 +1456,22 @@
     </row>
     <row r="23" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A23" s="6">
-        <v>10016</v>
+        <v>10315</v>
       </c>
       <c r="B23" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="C23" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D23" t="s">
         <v>9</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="F23" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="G23" s="9" t="b">
         <v>1</v>
@@ -1413,7 +1485,7 @@
     </row>
     <row r="24" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A24" s="6">
-        <v>10017</v>
+        <v>10188</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -1425,7 +1497,7 @@
         <v>9</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="F24" t="s">
         <v>10</v>
@@ -1442,7 +1514,7 @@
     </row>
     <row r="25" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A25" s="6">
-        <v>10018</v>
+        <v>10016</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -1454,7 +1526,7 @@
         <v>9</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="F25" t="s">
         <v>10</v>
@@ -1471,7 +1543,7 @@
     </row>
     <row r="26" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A26" s="6">
-        <v>10019</v>
+        <v>10017</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -1483,10 +1555,10 @@
         <v>9</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F26" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="G26" s="9" t="b">
         <v>1</v>
@@ -1500,7 +1572,7 @@
     </row>
     <row r="27" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A27" s="6">
-        <v>10020</v>
+        <v>10018</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -1512,10 +1584,10 @@
         <v>9</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F27" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="G27" s="9" t="b">
         <v>1</v>
@@ -1529,7 +1601,7 @@
     </row>
     <row r="28" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A28" s="6">
-        <v>10021</v>
+        <v>10019</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
@@ -1541,7 +1613,7 @@
         <v>9</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F28" t="s">
         <v>41</v>
@@ -1558,7 +1630,7 @@
     </row>
     <row r="29" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A29" s="6">
-        <v>10022</v>
+        <v>10020</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -1570,7 +1642,7 @@
         <v>9</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F29" t="s">
         <v>41</v>
@@ -1587,19 +1659,19 @@
     </row>
     <row r="30" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A30" s="6">
-        <v>10023</v>
+        <v>10021</v>
       </c>
       <c r="B30" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="C30" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="D30" t="s">
         <v>9</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="F30" t="s">
         <v>41</v>
@@ -1616,19 +1688,19 @@
     </row>
     <row r="31" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A31" s="6">
-        <v>10024</v>
+        <v>10022</v>
       </c>
       <c r="B31" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="D31" t="s">
         <v>9</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="F31" t="s">
         <v>41</v>
@@ -1645,7 +1717,7 @@
     </row>
     <row r="32" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A32" s="6">
-        <v>10025</v>
+        <v>10023</v>
       </c>
       <c r="B32" t="s">
         <v>35</v>
@@ -1657,7 +1729,7 @@
         <v>9</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F32" t="s">
         <v>41</v>
@@ -1672,9 +1744,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A33" s="6">
-        <v>10026</v>
+        <v>10024</v>
       </c>
       <c r="B33" t="s">
         <v>35</v>
@@ -1686,7 +1758,7 @@
         <v>9</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F33" t="s">
         <v>41</v>
@@ -1701,9 +1773,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A34" s="6">
-        <v>10089</v>
+        <v>10025</v>
       </c>
       <c r="B34" t="s">
         <v>35</v>
@@ -1715,7 +1787,7 @@
         <v>9</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F34" t="s">
         <v>41</v>
@@ -1730,9 +1802,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A35" s="6">
-        <v>10090</v>
+        <v>10026</v>
       </c>
       <c r="B35" t="s">
         <v>35</v>
@@ -1744,10 +1816,10 @@
         <v>9</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F35" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="G35" s="9" t="b">
         <v>1</v>
@@ -1759,9 +1831,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A36" s="6">
-        <v>10091</v>
+        <v>10089</v>
       </c>
       <c r="B36" t="s">
         <v>35</v>
@@ -1773,10 +1845,10 @@
         <v>9</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F36" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="G36" s="9" t="b">
         <v>1</v>
@@ -1788,9 +1860,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A37" s="6">
-        <v>10011</v>
+        <v>10090</v>
       </c>
       <c r="B37" t="s">
         <v>35</v>
@@ -1802,7 +1874,7 @@
         <v>9</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F37" t="s">
         <v>10</v>
@@ -1817,9 +1889,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A38" s="6">
-        <v>10123</v>
+        <v>10091</v>
       </c>
       <c r="B38" t="s">
         <v>35</v>
@@ -1831,7 +1903,7 @@
         <v>9</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F38" t="s">
         <v>10</v>
@@ -1846,9 +1918,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A39" s="6">
-        <v>10094</v>
+        <v>10011</v>
       </c>
       <c r="B39" t="s">
         <v>35</v>
@@ -1860,28 +1932,449 @@
         <v>9</v>
       </c>
       <c r="E39" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F39" t="s">
+        <v>10</v>
+      </c>
+      <c r="G39" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H39" t="s">
+        <v>11</v>
+      </c>
+      <c r="I39" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A40" s="6">
+        <v>10123</v>
+      </c>
+      <c r="B40" t="s">
+        <v>35</v>
+      </c>
+      <c r="C40" t="s">
+        <v>35</v>
+      </c>
+      <c r="D40" t="s">
+        <v>9</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F40" t="s">
+        <v>10</v>
+      </c>
+      <c r="G40" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" t="s">
+        <v>11</v>
+      </c>
+      <c r="I40" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A41" s="6">
+        <v>10094</v>
+      </c>
+      <c r="B41" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" t="s">
+        <v>35</v>
+      </c>
+      <c r="D41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F39" t="s">
-        <v>10</v>
-      </c>
-      <c r="G39" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H39" t="s">
-        <v>11</v>
-      </c>
-      <c r="I39" t="s">
-        <v>12</v>
-      </c>
+      <c r="F41" t="s">
+        <v>10</v>
+      </c>
+      <c r="G41" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H41" t="s">
+        <v>11</v>
+      </c>
+      <c r="I41" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A42" s="6">
+        <v>12001</v>
+      </c>
+      <c r="B42" t="s">
+        <v>60</v>
+      </c>
+      <c r="C42" t="s">
+        <v>60</v>
+      </c>
+      <c r="D42" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F42" t="s">
+        <v>10</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H42" t="s">
+        <v>62</v>
+      </c>
+      <c r="I42" t="s">
+        <v>12</v>
+      </c>
+      <c r="K42" s="10"/>
+    </row>
+    <row r="43" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A43" s="6">
+        <v>12002</v>
+      </c>
+      <c r="B43" t="s">
+        <v>60</v>
+      </c>
+      <c r="C43" t="s">
+        <v>60</v>
+      </c>
+      <c r="D43" t="s">
+        <v>9</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F43" t="s">
+        <v>41</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H43" t="s">
+        <v>62</v>
+      </c>
+      <c r="I43" t="s">
+        <v>12</v>
+      </c>
+      <c r="K43" s="10"/>
+    </row>
+    <row r="44" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A44" s="6">
+        <v>12003</v>
+      </c>
+      <c r="B44" t="s">
+        <v>60</v>
+      </c>
+      <c r="C44" t="s">
+        <v>60</v>
+      </c>
+      <c r="D44" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F44" t="s">
+        <v>10</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H44" t="s">
+        <v>62</v>
+      </c>
+      <c r="I44" t="s">
+        <v>12</v>
+      </c>
+      <c r="K44" s="10"/>
+    </row>
+    <row r="45" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A45" s="6">
+        <v>12004</v>
+      </c>
+      <c r="B45" t="s">
+        <v>60</v>
+      </c>
+      <c r="C45" t="s">
+        <v>60</v>
+      </c>
+      <c r="D45" t="s">
+        <v>9</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F45" t="s">
+        <v>41</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H45" t="s">
+        <v>62</v>
+      </c>
+      <c r="I45" t="s">
+        <v>12</v>
+      </c>
+      <c r="K45" s="10"/>
+    </row>
+    <row r="46" spans="1:11" ht="87" x14ac:dyDescent="0.35">
+      <c r="A46" s="6">
+        <v>12005</v>
+      </c>
+      <c r="B46" t="s">
+        <v>60</v>
+      </c>
+      <c r="C46" t="s">
+        <v>60</v>
+      </c>
+      <c r="D46" t="s">
+        <v>9</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F46" t="s">
+        <v>10</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H46" t="s">
+        <v>62</v>
+      </c>
+      <c r="I46" t="s">
+        <v>12</v>
+      </c>
+      <c r="K46" s="10"/>
+    </row>
+    <row r="47" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A47" s="6">
+        <v>12006</v>
+      </c>
+      <c r="B47" t="s">
+        <v>60</v>
+      </c>
+      <c r="C47" t="s">
+        <v>60</v>
+      </c>
+      <c r="D47" t="s">
+        <v>9</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F47" t="s">
+        <v>41</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H47" t="s">
+        <v>62</v>
+      </c>
+      <c r="I47" t="s">
+        <v>12</v>
+      </c>
+      <c r="K47" s="10"/>
+    </row>
+    <row r="48" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A48" s="6">
+        <v>11001</v>
+      </c>
+      <c r="B48" t="s">
+        <v>63</v>
+      </c>
+      <c r="C48" t="s">
+        <v>63</v>
+      </c>
+      <c r="D48" t="s">
+        <v>9</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F48" t="s">
+        <v>10</v>
+      </c>
+      <c r="G48" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H48" t="s">
+        <v>62</v>
+      </c>
+      <c r="I48" t="s">
+        <v>12</v>
+      </c>
+      <c r="K48" s="10"/>
+    </row>
+    <row r="49" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A49" s="6">
+        <v>11002</v>
+      </c>
+      <c r="B49" t="s">
+        <v>63</v>
+      </c>
+      <c r="C49" t="s">
+        <v>63</v>
+      </c>
+      <c r="D49" t="s">
+        <v>9</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F49" t="s">
+        <v>41</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H49" t="s">
+        <v>62</v>
+      </c>
+      <c r="I49" t="s">
+        <v>12</v>
+      </c>
+      <c r="K49" s="10"/>
+    </row>
+    <row r="50" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A50" s="6">
+        <v>11003</v>
+      </c>
+      <c r="B50" t="s">
+        <v>63</v>
+      </c>
+      <c r="C50" t="s">
+        <v>63</v>
+      </c>
+      <c r="D50" t="s">
+        <v>9</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F50" t="s">
+        <v>10</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H50" t="s">
+        <v>62</v>
+      </c>
+      <c r="I50" t="s">
+        <v>12</v>
+      </c>
+      <c r="K50" s="10"/>
+    </row>
+    <row r="51" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A51" s="6">
+        <v>11004</v>
+      </c>
+      <c r="B51" t="s">
+        <v>63</v>
+      </c>
+      <c r="C51" t="s">
+        <v>63</v>
+      </c>
+      <c r="D51" t="s">
+        <v>9</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F51" t="s">
+        <v>41</v>
+      </c>
+      <c r="G51" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H51" t="s">
+        <v>62</v>
+      </c>
+      <c r="I51" t="s">
+        <v>12</v>
+      </c>
+      <c r="K51" s="10"/>
+    </row>
+    <row r="52" spans="1:11" ht="87" x14ac:dyDescent="0.35">
+      <c r="A52" s="6">
+        <v>11005</v>
+      </c>
+      <c r="B52" t="s">
+        <v>63</v>
+      </c>
+      <c r="C52" t="s">
+        <v>63</v>
+      </c>
+      <c r="D52" t="s">
+        <v>9</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F52" t="s">
+        <v>10</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H52" t="s">
+        <v>62</v>
+      </c>
+      <c r="I52" t="s">
+        <v>12</v>
+      </c>
+      <c r="K52" s="10"/>
+    </row>
+    <row r="53" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A53" s="6">
+        <v>11006</v>
+      </c>
+      <c r="B53" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" t="s">
+        <v>63</v>
+      </c>
+      <c r="D53" t="s">
+        <v>9</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F53" t="s">
+        <v>41</v>
+      </c>
+      <c r="G53" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H53" t="s">
+        <v>62</v>
+      </c>
+      <c r="I53" t="s">
+        <v>12</v>
+      </c>
+      <c r="K53" s="10"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I39" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:I41" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A14:A39">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  <conditionalFormatting sqref="A14:A41">
+    <cfRule type="duplicateValues" dxfId="3" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/mosip_master/xlsx/dynamic_field.xlsx
+++ b/mosip_master/xlsx/dynamic_field.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\eclipse-workspace\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D9FC4F5-47A5-4FB6-A06F-356858ACB543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D13DAC-63F9-42CF-A3EC-6C9D7E348893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -233,20 +233,6 @@
   <si>
     <t xml:space="preserve">
 	{
-		"code": "MLE",
-		"value": "Macho"
-	}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-	{
-		"code": "FLE",
-		"value": "Fêmea"
-	}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-	{
 		"code": "101",
 		"value": "Solteiro(a)"
 	}</t>
@@ -389,6 +375,20 @@
 	"code": "US",
 	"value": "United States"
 }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+	{
+		"code": "MLE",
+		"value": "Masculino"
+	}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+	{
+		"code": "FLE",
+		"value": "Feminino"
+	}</t>
   </si>
 </sst>
 </file>
@@ -475,27 +475,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1309,7 +1289,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>10310</v>
       </c>
@@ -1338,7 +1318,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>10312</v>
       </c>
@@ -1367,7 +1347,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>10313</v>
       </c>
@@ -1396,7 +1376,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>10311</v>
       </c>
@@ -1439,7 +1419,7 @@
         <v>9</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="F22" t="s">
         <v>41</v>
@@ -1468,7 +1448,7 @@
         <v>9</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="F23" t="s">
         <v>41</v>
@@ -1555,7 +1535,7 @@
         <v>9</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F26" t="s">
         <v>10</v>
@@ -1584,7 +1564,7 @@
         <v>9</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F27" t="s">
         <v>10</v>
@@ -1613,7 +1593,7 @@
         <v>9</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F28" t="s">
         <v>41</v>
@@ -1642,7 +1622,7 @@
         <v>9</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F29" t="s">
         <v>41</v>
@@ -1671,7 +1651,7 @@
         <v>9</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F30" t="s">
         <v>41</v>
@@ -1700,7 +1680,7 @@
         <v>9</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F31" t="s">
         <v>41</v>
@@ -1729,7 +1709,7 @@
         <v>9</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F32" t="s">
         <v>41</v>
@@ -1758,7 +1738,7 @@
         <v>9</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F33" t="s">
         <v>41</v>
@@ -1787,7 +1767,7 @@
         <v>9</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F34" t="s">
         <v>41</v>
@@ -1816,7 +1796,7 @@
         <v>9</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F35" t="s">
         <v>41</v>
@@ -1845,7 +1825,7 @@
         <v>9</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F36" t="s">
         <v>41</v>
@@ -1874,7 +1854,7 @@
         <v>9</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F37" t="s">
         <v>10</v>
@@ -1903,7 +1883,7 @@
         <v>9</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F38" t="s">
         <v>10</v>
@@ -1932,7 +1912,7 @@
         <v>9</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F39" t="s">
         <v>10</v>
@@ -1961,7 +1941,7 @@
         <v>9</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F40" t="s">
         <v>10</v>
@@ -1990,7 +1970,7 @@
         <v>9</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F41" t="s">
         <v>10</v>
@@ -2010,25 +1990,25 @@
         <v>12001</v>
       </c>
       <c r="B42" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42" t="s">
+        <v>58</v>
+      </c>
+      <c r="D42" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F42" t="s">
+        <v>10</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="H42" t="s">
         <v>60</v>
-      </c>
-      <c r="C42" t="s">
-        <v>60</v>
-      </c>
-      <c r="D42" t="s">
-        <v>9</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F42" t="s">
-        <v>10</v>
-      </c>
-      <c r="G42" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="H42" t="s">
-        <v>62</v>
       </c>
       <c r="I42" t="s">
         <v>12</v>
@@ -2040,25 +2020,25 @@
         <v>12002</v>
       </c>
       <c r="B43" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C43" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D43" t="s">
         <v>9</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F43" t="s">
         <v>41</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H43" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I43" t="s">
         <v>12</v>
@@ -2070,25 +2050,25 @@
         <v>12003</v>
       </c>
       <c r="B44" t="s">
+        <v>58</v>
+      </c>
+      <c r="C44" t="s">
+        <v>58</v>
+      </c>
+      <c r="D44" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F44" t="s">
+        <v>10</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="H44" t="s">
         <v>60</v>
-      </c>
-      <c r="C44" t="s">
-        <v>60</v>
-      </c>
-      <c r="D44" t="s">
-        <v>9</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F44" t="s">
-        <v>10</v>
-      </c>
-      <c r="G44" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="H44" t="s">
-        <v>62</v>
       </c>
       <c r="I44" t="s">
         <v>12</v>
@@ -2100,25 +2080,25 @@
         <v>12004</v>
       </c>
       <c r="B45" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C45" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D45" t="s">
         <v>9</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F45" t="s">
         <v>41</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H45" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I45" t="s">
         <v>12</v>
@@ -2130,25 +2110,25 @@
         <v>12005</v>
       </c>
       <c r="B46" t="s">
+        <v>58</v>
+      </c>
+      <c r="C46" t="s">
+        <v>58</v>
+      </c>
+      <c r="D46" t="s">
+        <v>9</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F46" t="s">
+        <v>10</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="H46" t="s">
         <v>60</v>
-      </c>
-      <c r="C46" t="s">
-        <v>60</v>
-      </c>
-      <c r="D46" t="s">
-        <v>9</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F46" t="s">
-        <v>10</v>
-      </c>
-      <c r="G46" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="H46" t="s">
-        <v>62</v>
       </c>
       <c r="I46" t="s">
         <v>12</v>
@@ -2160,25 +2140,25 @@
         <v>12006</v>
       </c>
       <c r="B47" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C47" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D47" t="s">
         <v>9</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F47" t="s">
         <v>41</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H47" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I47" t="s">
         <v>12</v>
@@ -2190,25 +2170,25 @@
         <v>11001</v>
       </c>
       <c r="B48" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C48" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D48" t="s">
         <v>9</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F48" t="s">
         <v>10</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H48" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I48" t="s">
         <v>12</v>
@@ -2220,25 +2200,25 @@
         <v>11002</v>
       </c>
       <c r="B49" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C49" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D49" t="s">
         <v>9</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F49" t="s">
         <v>41</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H49" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I49" t="s">
         <v>12</v>
@@ -2250,25 +2230,25 @@
         <v>11003</v>
       </c>
       <c r="B50" t="s">
+        <v>61</v>
+      </c>
+      <c r="C50" t="s">
+        <v>61</v>
+      </c>
+      <c r="D50" t="s">
+        <v>9</v>
+      </c>
+      <c r="E50" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C50" t="s">
-        <v>63</v>
-      </c>
-      <c r="D50" t="s">
-        <v>9</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="F50" t="s">
         <v>10</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H50" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I50" t="s">
         <v>12</v>
@@ -2280,25 +2260,25 @@
         <v>11004</v>
       </c>
       <c r="B51" t="s">
+        <v>61</v>
+      </c>
+      <c r="C51" t="s">
+        <v>61</v>
+      </c>
+      <c r="D51" t="s">
+        <v>9</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="C51" t="s">
-        <v>63</v>
-      </c>
-      <c r="D51" t="s">
-        <v>9</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="F51" t="s">
         <v>41</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H51" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I51" t="s">
         <v>12</v>
@@ -2310,25 +2290,25 @@
         <v>11005</v>
       </c>
       <c r="B52" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C52" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D52" t="s">
         <v>9</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F52" t="s">
         <v>10</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H52" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I52" t="s">
         <v>12</v>
@@ -2340,25 +2320,25 @@
         <v>11006</v>
       </c>
       <c r="B53" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C53" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D53" t="s">
         <v>9</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F53" t="s">
         <v>41</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H53" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I53" t="s">
         <v>12</v>
@@ -2367,14 +2347,14 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I41" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <conditionalFormatting sqref="A1">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:A41">
-    <cfRule type="duplicateValues" dxfId="3" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
